--- a/accountant-skill/data/output/Mar2025/audit_validation_Mar2025.xlsx
+++ b/accountant-skill/data/output/Mar2025/audit_validation_Mar2025.xlsx
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-03-01 to 2025-03-31</t>
+          <t>2025-Mar-01 to 2025-Mar-31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Assets=400,965,043.31, Equity=400,965,043.31, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=840,495,866.31, Equity=840,495,866.31, Liabilities=0.00, Diff=-0.00</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-03-01 to 2025-03-31</t>
+          <t>2025-Mar-01 to 2025-Mar-31</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Assets=400,965,043.31, Equity=400,965,043.31, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=840,495,866.31, Equity=840,495,866.31, Liabilities=0.00, Diff=-0.00</t>
         </is>
       </c>
     </row>
